--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenCost.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenCost.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -163,9 +163,6 @@
     <t>1#10</t>
   </si>
   <si>
-    <t>2#11</t>
-  </si>
-  <si>
     <t>本次失败装备消失</t>
   </si>
   <si>
@@ -220,10 +217,13 @@
     <t>7#16</t>
   </si>
   <si>
-    <t>镶宝消耗</t>
+    <t>8#17</t>
   </si>
   <si>
     <t>9#18</t>
+  </si>
+  <si>
+    <t>镶宝消耗</t>
   </si>
   <si>
     <t>50030002#4|50030003#4|50030001#2</t>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>翅膀消耗（1代）</t>
+  </si>
+  <si>
+    <t>2#11</t>
   </si>
   <si>
     <t>翅膀消耗（2代）</t>
@@ -1365,7 +1368,7 @@
     <col min="13" max="13" width="40.5" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:13">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1551,7 +1554,9 @@
       <c r="G5" s="14">
         <v>10000</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
       <c r="K5" s="2"/>
@@ -1582,7 +1587,9 @@
       <c r="G6" s="14">
         <v>10000</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="14">
+        <v>1</v>
+      </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
       <c r="K6" s="2"/>
@@ -1613,7 +1620,9 @@
       <c r="G7" s="14">
         <v>8000</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="14">
+        <v>2</v>
+      </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="2"/>
@@ -1644,7 +1653,9 @@
       <c r="G8" s="14">
         <v>8000</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>3</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="2"/>
@@ -1675,7 +1686,9 @@
       <c r="G9" s="14">
         <v>8000</v>
       </c>
-      <c r="H9" s="14"/>
+      <c r="H9" s="14">
+        <v>4</v>
+      </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="2"/>
@@ -1706,6 +1719,9 @@
       <c r="G10" s="14">
         <v>8000</v>
       </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="2"/>
@@ -1731,18 +1747,20 @@
         <v>1</v>
       </c>
       <c r="F11" s="14">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="G11" s="14">
-        <v>7000</v>
-      </c>
-      <c r="H11" s="14"/>
+        <v>6500</v>
+      </c>
+      <c r="H11" s="14">
+        <v>5</v>
+      </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="17" t="s">
-        <v>43</v>
+      <c r="M11" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:13">
@@ -1767,13 +1785,15 @@
       <c r="G12" s="14">
         <v>6500</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="17" t="s">
-        <v>43</v>
+      <c r="M12" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:13">
@@ -1798,13 +1818,15 @@
       <c r="G13" s="14">
         <v>6500</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="17" t="s">
-        <v>43</v>
+      <c r="M13" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:13">
@@ -1829,18 +1851,20 @@
       <c r="G14" s="14">
         <v>6000</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="14">
+        <v>9</v>
+      </c>
       <c r="I14" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="M14" s="17"/>
     </row>
@@ -1867,19 +1891,19 @@
         <v>5500</v>
       </c>
       <c r="H15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M15" s="17"/>
     </row>
@@ -1906,19 +1930,19 @@
         <v>5500</v>
       </c>
       <c r="H16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M16" s="17"/>
     </row>
@@ -1945,19 +1969,19 @@
         <v>5000</v>
       </c>
       <c r="H17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M17" s="17"/>
     </row>
@@ -1984,19 +2008,19 @@
         <v>4000</v>
       </c>
       <c r="H18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M18" s="17"/>
     </row>
@@ -2023,19 +2047,19 @@
         <v>3000</v>
       </c>
       <c r="H19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="14">
         <v>1</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M19" s="17"/>
     </row>
@@ -2047,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="18">
         <v>1</v>
@@ -2061,7 +2085,9 @@
       <c r="G20" s="14">
         <v>10000</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="3"/>
@@ -2077,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="18">
         <v>2</v>
@@ -2091,7 +2117,9 @@
       <c r="G21" s="14">
         <v>10000</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="14">
+        <v>1</v>
+      </c>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="3"/>
@@ -2107,7 +2135,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="18">
         <v>3</v>
@@ -2121,7 +2149,9 @@
       <c r="G22" s="14">
         <v>8000</v>
       </c>
-      <c r="H22" s="18"/>
+      <c r="H22" s="14">
+        <v>2</v>
+      </c>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
       <c r="K22" s="3"/>
@@ -2137,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" s="18">
         <v>4</v>
@@ -2151,7 +2181,9 @@
       <c r="G23" s="14">
         <v>8000</v>
       </c>
-      <c r="H23" s="18"/>
+      <c r="H23" s="14">
+        <v>3</v>
+      </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="3"/>
@@ -2167,7 +2199,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="18">
         <v>5</v>
@@ -2181,7 +2213,9 @@
       <c r="G24" s="14">
         <v>8000</v>
       </c>
-      <c r="H24" s="18"/>
+      <c r="H24" s="14">
+        <v>4</v>
+      </c>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="3"/>
@@ -2197,7 +2231,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="18">
         <v>6</v>
@@ -2211,7 +2245,9 @@
       <c r="G25" s="14">
         <v>8000</v>
       </c>
-      <c r="H25" s="3"/>
+      <c r="H25" s="2">
+        <v>5</v>
+      </c>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
       <c r="K25" s="3"/>
@@ -2227,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="18">
         <v>7</v>
@@ -2236,17 +2272,19 @@
         <v>1</v>
       </c>
       <c r="F26" s="14">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="G26" s="14">
-        <v>7000</v>
-      </c>
-      <c r="H26" s="18"/>
+        <v>6500</v>
+      </c>
+      <c r="H26" s="14">
+        <v>5</v>
+      </c>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="3"/>
       <c r="M26" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:13">
@@ -2257,7 +2295,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="18">
         <v>8</v>
@@ -2271,12 +2309,14 @@
       <c r="G27" s="14">
         <v>6500</v>
       </c>
-      <c r="H27" s="18"/>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
       <c r="K27" s="3"/>
       <c r="M27" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:13">
@@ -2287,7 +2327,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="18">
         <v>9</v>
@@ -2301,12 +2341,14 @@
       <c r="G28" s="14">
         <v>6500</v>
       </c>
-      <c r="H28" s="18"/>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
       <c r="K28" s="3"/>
       <c r="M28" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:13">
@@ -2317,7 +2359,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="18">
         <v>10</v>
@@ -2331,18 +2373,20 @@
       <c r="G29" s="14">
         <v>6000</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="14">
+        <v>9</v>
+      </c>
       <c r="I29" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M29" s="20"/>
     </row>
@@ -2354,7 +2398,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="18">
         <v>11</v>
@@ -2369,19 +2413,19 @@
         <v>5500</v>
       </c>
       <c r="H30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M30" s="20"/>
     </row>
@@ -2393,7 +2437,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="18">
         <v>12</v>
@@ -2408,19 +2452,19 @@
         <v>5500</v>
       </c>
       <c r="H31" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M31" s="20"/>
     </row>
@@ -2432,7 +2476,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="18">
         <v>13</v>
@@ -2447,19 +2491,19 @@
         <v>5000</v>
       </c>
       <c r="H32" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M32" s="20"/>
     </row>
@@ -2471,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="18">
         <v>14</v>
@@ -2486,19 +2530,19 @@
         <v>4000</v>
       </c>
       <c r="H33" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I33" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M33" s="20"/>
     </row>
@@ -2510,7 +2554,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" s="18">
         <v>15</v>
@@ -2525,19 +2569,19 @@
         <v>3000</v>
       </c>
       <c r="H34" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="14">
         <v>1</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M34" s="20"/>
     </row>
@@ -2549,7 +2593,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="21">
         <v>1</v>
@@ -2563,7 +2607,9 @@
       <c r="G35" s="14">
         <v>10000</v>
       </c>
-      <c r="H35" s="21"/>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
       <c r="K35" s="4"/>
@@ -2579,7 +2625,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="21">
         <v>2</v>
@@ -2593,7 +2639,9 @@
       <c r="G36" s="14">
         <v>10000</v>
       </c>
-      <c r="H36" s="21"/>
+      <c r="H36" s="14">
+        <v>1</v>
+      </c>
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
       <c r="K36" s="4"/>
@@ -2609,7 +2657,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D37" s="21">
         <v>3</v>
@@ -2623,7 +2671,9 @@
       <c r="G37" s="14">
         <v>8000</v>
       </c>
-      <c r="H37" s="21"/>
+      <c r="H37" s="14">
+        <v>2</v>
+      </c>
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
       <c r="K37" s="4"/>
@@ -2639,7 +2689,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" s="21">
         <v>4</v>
@@ -2653,7 +2703,9 @@
       <c r="G38" s="14">
         <v>7500</v>
       </c>
-      <c r="H38" s="21"/>
+      <c r="H38" s="14">
+        <v>3</v>
+      </c>
       <c r="I38" s="21"/>
       <c r="J38" s="21"/>
       <c r="K38" s="4"/>
@@ -2669,7 +2721,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="21">
         <v>5</v>
@@ -2683,7 +2735,9 @@
       <c r="G39" s="14">
         <v>7500</v>
       </c>
-      <c r="H39" s="21"/>
+      <c r="H39" s="14">
+        <v>4</v>
+      </c>
       <c r="I39" s="21"/>
       <c r="J39" s="21"/>
       <c r="K39" s="4"/>
@@ -2699,7 +2753,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D40" s="21">
         <v>6</v>
@@ -2713,7 +2767,9 @@
       <c r="G40" s="14">
         <v>7000</v>
       </c>
-      <c r="H40" s="4"/>
+      <c r="H40" s="2">
+        <v>5</v>
+      </c>
       <c r="I40" s="21"/>
       <c r="J40" s="21"/>
       <c r="K40" s="4"/>
@@ -2729,7 +2785,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41" s="21">
         <v>7</v>
@@ -2738,17 +2794,19 @@
         <v>1</v>
       </c>
       <c r="F41" s="14">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="G41" s="14">
-        <v>6500</v>
-      </c>
-      <c r="H41" s="21"/>
+        <v>5000</v>
+      </c>
+      <c r="H41" s="14">
+        <v>5</v>
+      </c>
       <c r="I41" s="21"/>
       <c r="J41" s="21"/>
       <c r="K41" s="4"/>
       <c r="M41" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" spans="1:13">
@@ -2759,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="21">
         <v>8</v>
@@ -2773,7 +2831,9 @@
       <c r="G42" s="14">
         <v>6500</v>
       </c>
-      <c r="H42" s="21"/>
+      <c r="H42" s="14">
+        <v>0</v>
+      </c>
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
       <c r="K42" s="4"/>
@@ -2789,7 +2849,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D43" s="21">
         <v>9</v>
@@ -2803,12 +2863,14 @@
       <c r="G43" s="14">
         <v>6000</v>
       </c>
-      <c r="H43" s="21"/>
+      <c r="H43" s="14">
+        <v>0</v>
+      </c>
       <c r="I43" s="21"/>
       <c r="J43" s="21"/>
       <c r="K43" s="4"/>
       <c r="M43" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" s="4" customFormat="1" spans="1:13">
@@ -2819,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" s="21">
         <v>10</v>
@@ -2833,18 +2895,20 @@
       <c r="G44" s="14">
         <v>5500</v>
       </c>
-      <c r="H44" s="14"/>
+      <c r="H44" s="14">
+        <v>9</v>
+      </c>
       <c r="I44" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M44" s="23"/>
     </row>
@@ -2856,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" s="21">
         <v>11</v>
@@ -2871,19 +2935,19 @@
         <v>5500</v>
       </c>
       <c r="H45" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M45" s="23"/>
     </row>
@@ -2895,7 +2959,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="21">
         <v>12</v>
@@ -2910,19 +2974,19 @@
         <v>5000</v>
       </c>
       <c r="H46" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M46" s="23"/>
     </row>
@@ -2934,7 +2998,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D47" s="21">
         <v>13</v>
@@ -2949,19 +3013,19 @@
         <v>4500</v>
       </c>
       <c r="H47" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" s="14">
         <v>1</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M47" s="23"/>
     </row>
@@ -2973,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D48" s="21">
         <v>14</v>
@@ -2988,19 +3052,19 @@
         <v>4000</v>
       </c>
       <c r="H48" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I48" s="14">
         <v>1</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M48" s="23"/>
     </row>
@@ -3012,7 +3076,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="21">
         <v>15</v>
@@ -3027,19 +3091,19 @@
         <v>3000</v>
       </c>
       <c r="H49" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="14">
         <v>1</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M49" s="23"/>
     </row>
@@ -3051,7 +3115,7 @@
         <v>6</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D50" s="24">
         <v>1</v>
@@ -3077,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D51" s="24">
         <v>2</v>
@@ -3103,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" s="24">
         <v>3</v>
@@ -3129,7 +3193,7 @@
         <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D53" s="24">
         <v>4</v>
@@ -3155,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D54" s="24">
         <v>5</v>
@@ -3165,7 +3229,7 @@
       </c>
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
       <c r="K54" s="5"/>
@@ -3181,7 +3245,7 @@
         <v>6</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D55" s="24">
         <v>6</v>
@@ -3191,7 +3255,7 @@
       </c>
       <c r="F55" s="24"/>
       <c r="G55" s="24"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="14"/>
       <c r="I55" s="24"/>
       <c r="J55" s="24"/>
       <c r="K55" s="5"/>
@@ -3207,7 +3271,7 @@
         <v>6</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D56" s="24">
         <v>7</v>
@@ -3217,12 +3281,12 @@
       </c>
       <c r="F56" s="24"/>
       <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="24"/>
       <c r="J56" s="24"/>
       <c r="K56" s="5"/>
       <c r="M56" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" s="5" customFormat="1" spans="1:13">
@@ -3233,7 +3297,7 @@
         <v>6</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D57" s="24">
         <v>8</v>
@@ -3243,12 +3307,12 @@
       </c>
       <c r="F57" s="24"/>
       <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
+      <c r="H57" s="14"/>
       <c r="I57" s="24"/>
       <c r="J57" s="24"/>
       <c r="K57" s="5"/>
       <c r="M57" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" s="5" customFormat="1" spans="1:13">
@@ -3259,7 +3323,7 @@
         <v>6</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D58" s="24">
         <v>9</v>
@@ -3269,12 +3333,12 @@
       </c>
       <c r="F58" s="24"/>
       <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
+      <c r="H58" s="14"/>
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
       <c r="K58" s="5"/>
       <c r="M58" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" s="5" customFormat="1" spans="1:13">
@@ -3285,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D59" s="24">
         <v>10</v>
@@ -3299,18 +3363,20 @@
       <c r="G59" s="24">
         <v>5000</v>
       </c>
-      <c r="H59" s="14"/>
+      <c r="H59" s="14">
+        <v>9</v>
+      </c>
       <c r="I59" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K59" s="5" t="s">
         <v>64</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M59" s="26"/>
     </row>
@@ -3322,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D60" s="24">
         <v>11</v>
@@ -3337,19 +3403,19 @@
         <v>5000</v>
       </c>
       <c r="H60" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I60" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>65</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M60" s="26"/>
     </row>
@@ -3361,7 +3427,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D61" s="24">
         <v>12</v>
@@ -3376,19 +3442,19 @@
         <v>4500</v>
       </c>
       <c r="H61" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I61" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K61" s="5" t="s">
         <v>66</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M61" s="26"/>
     </row>
@@ -3400,7 +3466,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D62" s="24">
         <v>13</v>
@@ -3415,19 +3481,19 @@
         <v>4500</v>
       </c>
       <c r="H62" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I62" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>67</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M62" s="26"/>
     </row>
@@ -3439,7 +3505,7 @@
         <v>6</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D63" s="24">
         <v>14</v>
@@ -3454,19 +3520,19 @@
         <v>4000</v>
       </c>
       <c r="H63" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I63" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K63" s="5" t="s">
         <v>68</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M63" s="26"/>
     </row>
@@ -3478,7 +3544,7 @@
         <v>6</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D64" s="24">
         <v>15</v>
@@ -3493,19 +3559,19 @@
         <v>4000</v>
       </c>
       <c r="H64" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I64" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>69</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M64" s="26"/>
     </row>
@@ -3531,7 +3597,9 @@
       <c r="G65" s="14">
         <v>10000</v>
       </c>
-      <c r="H65" s="27"/>
+      <c r="H65" s="14">
+        <v>0</v>
+      </c>
       <c r="I65" s="27"/>
       <c r="J65" s="27"/>
       <c r="K65" s="27"/>
@@ -3562,7 +3630,9 @@
       <c r="G66" s="14">
         <v>10000</v>
       </c>
-      <c r="H66" s="27"/>
+      <c r="H66" s="14">
+        <v>1</v>
+      </c>
       <c r="I66" s="27"/>
       <c r="J66" s="27"/>
       <c r="K66" s="27"/>
@@ -3593,7 +3663,9 @@
       <c r="G67" s="14">
         <v>8000</v>
       </c>
-      <c r="H67" s="27"/>
+      <c r="H67" s="14">
+        <v>2</v>
+      </c>
       <c r="I67" s="27"/>
       <c r="J67" s="27"/>
       <c r="K67" s="27"/>
@@ -3624,7 +3696,9 @@
       <c r="G68" s="14">
         <v>7500</v>
       </c>
-      <c r="H68" s="27"/>
+      <c r="H68" s="14">
+        <v>3</v>
+      </c>
       <c r="I68" s="27"/>
       <c r="J68" s="27"/>
       <c r="K68" s="27"/>
@@ -3655,7 +3729,9 @@
       <c r="G69" s="14">
         <v>7500</v>
       </c>
-      <c r="H69" s="27"/>
+      <c r="H69" s="14">
+        <v>4</v>
+      </c>
       <c r="I69" s="27"/>
       <c r="J69" s="27"/>
       <c r="K69" s="27"/>
@@ -3686,7 +3762,9 @@
       <c r="G70" s="14">
         <v>7000</v>
       </c>
-      <c r="H70" s="27"/>
+      <c r="H70" s="2">
+        <v>5</v>
+      </c>
       <c r="I70" s="27"/>
       <c r="J70" s="27"/>
       <c r="K70" s="27"/>
@@ -3717,13 +3795,15 @@
       <c r="G71" s="14">
         <v>6500</v>
       </c>
-      <c r="H71" s="27"/>
+      <c r="H71" s="14">
+        <v>5</v>
+      </c>
       <c r="I71" s="27"/>
       <c r="J71" s="27"/>
       <c r="K71" s="27"/>
       <c r="L71" s="6"/>
       <c r="M71" s="29" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" s="6" customFormat="1" spans="1:13">
@@ -3748,13 +3828,15 @@
       <c r="G72" s="14">
         <v>6500</v>
       </c>
-      <c r="H72" s="27"/>
+      <c r="H72" s="14">
+        <v>0</v>
+      </c>
       <c r="I72" s="27"/>
       <c r="J72" s="27"/>
       <c r="K72" s="27"/>
       <c r="L72" s="6"/>
       <c r="M72" s="29" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" s="6" customFormat="1" spans="1:13">
@@ -3779,13 +3861,15 @@
       <c r="G73" s="14">
         <v>6000</v>
       </c>
-      <c r="H73" s="27"/>
+      <c r="H73" s="14">
+        <v>0</v>
+      </c>
       <c r="I73" s="27"/>
       <c r="J73" s="27"/>
       <c r="K73" s="27"/>
       <c r="L73" s="6"/>
       <c r="M73" s="29" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" s="6" customFormat="1" spans="1:13">
@@ -3810,18 +3894,20 @@
       <c r="G74" s="14">
         <v>5500</v>
       </c>
-      <c r="H74" s="14"/>
+      <c r="H74" s="14">
+        <v>9</v>
+      </c>
       <c r="I74" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M74" s="29"/>
     </row>
@@ -3848,19 +3934,19 @@
         <v>5500</v>
       </c>
       <c r="H75" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I75" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M75" s="29"/>
     </row>
@@ -3887,19 +3973,19 @@
         <v>5000</v>
       </c>
       <c r="H76" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I76" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M76" s="29"/>
     </row>
@@ -3926,19 +4012,19 @@
         <v>4500</v>
       </c>
       <c r="H77" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I77" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M77" s="29"/>
     </row>
@@ -3965,19 +4051,19 @@
         <v>4000</v>
       </c>
       <c r="H78" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I78" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M78" s="29"/>
     </row>
@@ -4004,19 +4090,19 @@
         <v>3000</v>
       </c>
       <c r="H79" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I79" s="14">
         <v>1</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M79" s="29"/>
     </row>
@@ -4028,7 +4114,7 @@
         <v>7</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D80" s="18">
         <v>1</v>
@@ -4042,7 +4128,9 @@
       <c r="G80" s="14">
         <v>10000</v>
       </c>
-      <c r="H80" s="18"/>
+      <c r="H80" s="14">
+        <v>0</v>
+      </c>
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
       <c r="K80" s="18"/>
@@ -4058,7 +4146,7 @@
         <v>7</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D81" s="18">
         <v>2</v>
@@ -4072,7 +4160,9 @@
       <c r="G81" s="14">
         <v>10000</v>
       </c>
-      <c r="H81" s="18"/>
+      <c r="H81" s="14">
+        <v>1</v>
+      </c>
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18"/>
@@ -4088,7 +4178,7 @@
         <v>7</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D82" s="18">
         <v>3</v>
@@ -4102,7 +4192,9 @@
       <c r="G82" s="14">
         <v>8000</v>
       </c>
-      <c r="H82" s="18"/>
+      <c r="H82" s="14">
+        <v>2</v>
+      </c>
       <c r="I82" s="18"/>
       <c r="J82" s="18"/>
       <c r="K82" s="18"/>
@@ -4118,7 +4210,7 @@
         <v>7</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D83" s="18">
         <v>4</v>
@@ -4132,7 +4224,9 @@
       <c r="G83" s="14">
         <v>7500</v>
       </c>
-      <c r="H83" s="18"/>
+      <c r="H83" s="14">
+        <v>3</v>
+      </c>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
       <c r="K83" s="18"/>
@@ -4148,7 +4242,7 @@
         <v>7</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D84" s="18">
         <v>5</v>
@@ -4162,7 +4256,9 @@
       <c r="G84" s="14">
         <v>7500</v>
       </c>
-      <c r="H84" s="18"/>
+      <c r="H84" s="14">
+        <v>4</v>
+      </c>
       <c r="I84" s="18"/>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
@@ -4178,7 +4274,7 @@
         <v>7</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D85" s="18">
         <v>6</v>
@@ -4192,7 +4288,9 @@
       <c r="G85" s="14">
         <v>7000</v>
       </c>
-      <c r="H85" s="18"/>
+      <c r="H85" s="2">
+        <v>5</v>
+      </c>
       <c r="I85" s="18"/>
       <c r="J85" s="18"/>
       <c r="K85" s="18"/>
@@ -4208,7 +4306,7 @@
         <v>7</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D86" s="18">
         <v>7</v>
@@ -4222,12 +4320,14 @@
       <c r="G86" s="14">
         <v>6500</v>
       </c>
-      <c r="H86" s="18"/>
+      <c r="H86" s="14">
+        <v>5</v>
+      </c>
       <c r="I86" s="18"/>
       <c r="J86" s="18"/>
       <c r="K86" s="18"/>
       <c r="M86" s="20" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" s="3" customFormat="1" spans="1:13">
@@ -4238,7 +4338,7 @@
         <v>7</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D87" s="18">
         <v>8</v>
@@ -4252,12 +4352,14 @@
       <c r="G87" s="14">
         <v>6500</v>
       </c>
-      <c r="H87" s="18"/>
+      <c r="H87" s="14">
+        <v>0</v>
+      </c>
       <c r="I87" s="18"/>
       <c r="J87" s="18"/>
       <c r="K87" s="18"/>
       <c r="M87" s="20" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88" s="3" customFormat="1" spans="1:13">
@@ -4268,7 +4370,7 @@
         <v>7</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D88" s="18">
         <v>9</v>
@@ -4282,12 +4384,14 @@
       <c r="G88" s="14">
         <v>6000</v>
       </c>
-      <c r="H88" s="18"/>
+      <c r="H88" s="14">
+        <v>0</v>
+      </c>
       <c r="I88" s="18"/>
       <c r="J88" s="18"/>
       <c r="K88" s="18"/>
       <c r="M88" s="20" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" s="3" customFormat="1" spans="1:13">
@@ -4298,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D89" s="18">
         <v>10</v>
@@ -4312,18 +4416,20 @@
       <c r="G89" s="14">
         <v>5500</v>
       </c>
-      <c r="H89" s="14"/>
+      <c r="H89" s="14">
+        <v>9</v>
+      </c>
       <c r="I89" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M89" s="20"/>
     </row>
@@ -4335,7 +4441,7 @@
         <v>7</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D90" s="18">
         <v>11</v>
@@ -4350,19 +4456,19 @@
         <v>5500</v>
       </c>
       <c r="H90" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I90" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M90" s="20"/>
     </row>
@@ -4374,7 +4480,7 @@
         <v>7</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D91" s="18">
         <v>12</v>
@@ -4389,19 +4495,19 @@
         <v>5000</v>
       </c>
       <c r="H91" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I91" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M91" s="20"/>
     </row>
@@ -4413,7 +4519,7 @@
         <v>7</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D92" s="18">
         <v>13</v>
@@ -4428,19 +4534,19 @@
         <v>4500</v>
       </c>
       <c r="H92" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I92" s="14">
         <v>1</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M92" s="20"/>
     </row>
@@ -4452,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D93" s="18">
         <v>14</v>
@@ -4467,19 +4573,19 @@
         <v>4000</v>
       </c>
       <c r="H93" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I93" s="14">
         <v>1</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M93" s="20"/>
     </row>
@@ -4491,7 +4597,7 @@
         <v>7</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D94" s="18">
         <v>15</v>
@@ -4506,19 +4612,19 @@
         <v>3000</v>
       </c>
       <c r="H94" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I94" s="14">
         <v>1</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M94" s="20"/>
     </row>
@@ -4530,7 +4636,7 @@
         <v>8</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D95" s="24">
         <v>1</v>
@@ -4544,7 +4650,9 @@
       <c r="G95" s="14">
         <v>10000</v>
       </c>
-      <c r="H95" s="24"/>
+      <c r="H95" s="14">
+        <v>0</v>
+      </c>
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
       <c r="K95" s="24"/>
@@ -4560,7 +4668,7 @@
         <v>8</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D96" s="24">
         <v>2</v>
@@ -4574,7 +4682,9 @@
       <c r="G96" s="14">
         <v>10000</v>
       </c>
-      <c r="H96" s="24"/>
+      <c r="H96" s="14">
+        <v>1</v>
+      </c>
       <c r="I96" s="24"/>
       <c r="J96" s="24"/>
       <c r="K96" s="24"/>
@@ -4590,7 +4700,7 @@
         <v>8</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D97" s="24">
         <v>3</v>
@@ -4604,7 +4714,9 @@
       <c r="G97" s="14">
         <v>8000</v>
       </c>
-      <c r="H97" s="24"/>
+      <c r="H97" s="14">
+        <v>2</v>
+      </c>
       <c r="I97" s="24"/>
       <c r="J97" s="24"/>
       <c r="K97" s="24"/>
@@ -4620,7 +4732,7 @@
         <v>8</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D98" s="24">
         <v>4</v>
@@ -4634,7 +4746,9 @@
       <c r="G98" s="14">
         <v>7500</v>
       </c>
-      <c r="H98" s="24"/>
+      <c r="H98" s="14">
+        <v>3</v>
+      </c>
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
       <c r="K98" s="24"/>
@@ -4650,7 +4764,7 @@
         <v>8</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D99" s="24">
         <v>5</v>
@@ -4664,7 +4778,9 @@
       <c r="G99" s="14">
         <v>7500</v>
       </c>
-      <c r="H99" s="24"/>
+      <c r="H99" s="14">
+        <v>4</v>
+      </c>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
       <c r="K99" s="24"/>
@@ -4680,7 +4796,7 @@
         <v>8</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D100" s="24">
         <v>6</v>
@@ -4694,7 +4810,9 @@
       <c r="G100" s="14">
         <v>7000</v>
       </c>
-      <c r="H100" s="24"/>
+      <c r="H100" s="2">
+        <v>5</v>
+      </c>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
       <c r="K100" s="24"/>
@@ -4710,7 +4828,7 @@
         <v>8</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D101" s="24">
         <v>7</v>
@@ -4724,12 +4842,14 @@
       <c r="G101" s="14">
         <v>6500</v>
       </c>
-      <c r="H101" s="24"/>
+      <c r="H101" s="14">
+        <v>5</v>
+      </c>
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
       <c r="K101" s="24"/>
       <c r="M101" s="26" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" s="5" customFormat="1" spans="1:13">
@@ -4740,7 +4860,7 @@
         <v>8</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D102" s="24">
         <v>8</v>
@@ -4754,12 +4874,14 @@
       <c r="G102" s="14">
         <v>6500</v>
       </c>
-      <c r="H102" s="24"/>
+      <c r="H102" s="14">
+        <v>0</v>
+      </c>
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
       <c r="K102" s="24"/>
       <c r="M102" s="26" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" s="5" customFormat="1" spans="1:13">
@@ -4770,7 +4892,7 @@
         <v>8</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D103" s="24">
         <v>9</v>
@@ -4784,12 +4906,14 @@
       <c r="G103" s="14">
         <v>6000</v>
       </c>
-      <c r="H103" s="24"/>
+      <c r="H103" s="14">
+        <v>0</v>
+      </c>
       <c r="I103" s="24"/>
       <c r="J103" s="24"/>
       <c r="K103" s="24"/>
       <c r="M103" s="26" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" s="5" customFormat="1" spans="1:13">
@@ -4800,7 +4924,7 @@
         <v>8</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D104" s="24">
         <v>10</v>
@@ -4814,18 +4938,20 @@
       <c r="G104" s="14">
         <v>5500</v>
       </c>
-      <c r="H104" s="14"/>
+      <c r="H104" s="14">
+        <v>9</v>
+      </c>
       <c r="I104" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M104" s="26"/>
     </row>
@@ -4837,7 +4963,7 @@
         <v>8</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D105" s="24">
         <v>11</v>
@@ -4852,19 +4978,19 @@
         <v>5500</v>
       </c>
       <c r="H105" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I105" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M105" s="26"/>
     </row>
@@ -4876,7 +5002,7 @@
         <v>8</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D106" s="24">
         <v>12</v>
@@ -4891,19 +5017,19 @@
         <v>5000</v>
       </c>
       <c r="H106" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I106" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M106" s="26"/>
     </row>
@@ -4915,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D107" s="24">
         <v>13</v>
@@ -4930,19 +5056,19 @@
         <v>4500</v>
       </c>
       <c r="H107" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I107" s="14">
         <v>1</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M107" s="26"/>
     </row>
@@ -4954,7 +5080,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D108" s="24">
         <v>14</v>
@@ -4969,19 +5095,19 @@
         <v>4000</v>
       </c>
       <c r="H108" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I108" s="14">
         <v>1</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M108" s="26"/>
     </row>
@@ -4993,7 +5119,7 @@
         <v>8</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D109" s="24">
         <v>15</v>
@@ -5008,19 +5134,19 @@
         <v>3000</v>
       </c>
       <c r="H109" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I109" s="14">
         <v>1</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M109" s="26"/>
     </row>
@@ -5032,7 +5158,7 @@
         <v>9</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D110" s="30">
         <v>1</v>
@@ -5046,7 +5172,9 @@
       <c r="G110" s="14">
         <v>10000</v>
       </c>
-      <c r="H110" s="30"/>
+      <c r="H110" s="14">
+        <v>0</v>
+      </c>
       <c r="I110" s="30"/>
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
@@ -5062,7 +5190,7 @@
         <v>9</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D111" s="30">
         <v>2</v>
@@ -5076,7 +5204,9 @@
       <c r="G111" s="14">
         <v>10000</v>
       </c>
-      <c r="H111" s="30"/>
+      <c r="H111" s="14">
+        <v>1</v>
+      </c>
       <c r="I111" s="30"/>
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
@@ -5092,7 +5222,7 @@
         <v>9</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D112" s="30">
         <v>3</v>
@@ -5106,7 +5236,9 @@
       <c r="G112" s="14">
         <v>8000</v>
       </c>
-      <c r="H112" s="30"/>
+      <c r="H112" s="14">
+        <v>2</v>
+      </c>
       <c r="I112" s="30"/>
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
@@ -5122,7 +5254,7 @@
         <v>9</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D113" s="30">
         <v>4</v>
@@ -5136,7 +5268,9 @@
       <c r="G113" s="14">
         <v>7500</v>
       </c>
-      <c r="H113" s="30"/>
+      <c r="H113" s="14">
+        <v>3</v>
+      </c>
       <c r="I113" s="30"/>
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
@@ -5152,7 +5286,7 @@
         <v>9</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D114" s="30">
         <v>5</v>
@@ -5166,7 +5300,9 @@
       <c r="G114" s="14">
         <v>7500</v>
       </c>
-      <c r="H114" s="30"/>
+      <c r="H114" s="14">
+        <v>4</v>
+      </c>
       <c r="I114" s="30"/>
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
@@ -5182,7 +5318,7 @@
         <v>9</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D115" s="30">
         <v>6</v>
@@ -5196,7 +5332,9 @@
       <c r="G115" s="14">
         <v>7000</v>
       </c>
-      <c r="H115" s="30"/>
+      <c r="H115" s="2">
+        <v>5</v>
+      </c>
       <c r="I115" s="30"/>
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
@@ -5212,7 +5350,7 @@
         <v>9</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D116" s="30">
         <v>7</v>
@@ -5226,12 +5364,14 @@
       <c r="G116" s="14">
         <v>6500</v>
       </c>
-      <c r="H116" s="30"/>
+      <c r="H116" s="14">
+        <v>5</v>
+      </c>
       <c r="I116" s="30"/>
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
       <c r="M116" s="32" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117" s="7" customFormat="1" spans="1:13">
@@ -5242,7 +5382,7 @@
         <v>9</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D117" s="30">
         <v>8</v>
@@ -5256,12 +5396,14 @@
       <c r="G117" s="14">
         <v>6500</v>
       </c>
-      <c r="H117" s="30"/>
+      <c r="H117" s="14">
+        <v>0</v>
+      </c>
       <c r="I117" s="30"/>
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
       <c r="M117" s="32" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118" s="7" customFormat="1" spans="1:13">
@@ -5272,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D118" s="30">
         <v>9</v>
@@ -5286,12 +5428,14 @@
       <c r="G118" s="14">
         <v>6000</v>
       </c>
-      <c r="H118" s="30"/>
+      <c r="H118" s="14">
+        <v>0</v>
+      </c>
       <c r="I118" s="30"/>
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
       <c r="M118" s="32" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" s="7" customFormat="1" spans="1:13">
@@ -5302,7 +5446,7 @@
         <v>9</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D119" s="30">
         <v>10</v>
@@ -5316,18 +5460,20 @@
       <c r="G119" s="14">
         <v>5500</v>
       </c>
-      <c r="H119" s="14"/>
+      <c r="H119" s="14">
+        <v>9</v>
+      </c>
       <c r="I119" s="14">
         <v>1</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M119" s="32"/>
     </row>
@@ -5339,7 +5485,7 @@
         <v>9</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D120" s="30">
         <v>11</v>
@@ -5354,19 +5500,19 @@
         <v>5500</v>
       </c>
       <c r="H120" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I120" s="14">
         <v>1</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M120" s="32"/>
     </row>
@@ -5378,7 +5524,7 @@
         <v>9</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D121" s="30">
         <v>12</v>
@@ -5393,19 +5539,19 @@
         <v>5000</v>
       </c>
       <c r="H121" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I121" s="14">
         <v>1</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M121" s="32"/>
     </row>
@@ -5417,7 +5563,7 @@
         <v>9</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D122" s="30">
         <v>13</v>
@@ -5432,19 +5578,19 @@
         <v>4500</v>
       </c>
       <c r="H122" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I122" s="14">
         <v>1</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M122" s="32"/>
     </row>
@@ -5456,7 +5602,7 @@
         <v>9</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D123" s="30">
         <v>14</v>
@@ -5471,19 +5617,19 @@
         <v>4000</v>
       </c>
       <c r="H123" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I123" s="14">
         <v>1</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M123" s="32"/>
     </row>
@@ -5495,7 +5641,7 @@
         <v>9</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D124" s="30">
         <v>15</v>
@@ -5510,19 +5656,19 @@
         <v>3000</v>
       </c>
       <c r="H124" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I124" s="14">
         <v>1</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M124" s="32"/>
     </row>
